--- a/artfynd/A 37438-2021 artfynd.xlsx
+++ b/artfynd/A 37438-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37438-2021 artfynd.xlsx
+++ b/artfynd/A 37438-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95503476</v>
+        <v>95504981</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,10 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591590.0879378035</v>
+        <v>592063</v>
       </c>
       <c r="R2" t="n">
-        <v>6428792.104066458</v>
+        <v>6428536</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,11 +768,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,54 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95504946</v>
+        <v>95505000</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -865,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591993.6470620979</v>
+        <v>592054</v>
       </c>
       <c r="R3" t="n">
-        <v>6428571.749772112</v>
+        <v>6428560</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -911,11 +888,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 + 3</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,69 +915,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95504253</v>
+        <v>113670105</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A37438, Troserum, V Ed, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592082.7741049519</v>
+        <v>591638</v>
       </c>
       <c r="R4" t="n">
-        <v>6428554.711398588</v>
+        <v>6428563</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,27 +988,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3 blommor</t>
+          <t>Mkt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,7 +1007,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1070,49 +1018,44 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95504230</v>
+        <v>113668913</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220686</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1120,26 +1063,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A37438, Troserum, V Ed, Sm</t>
+          <t>A 62464-2023 Troserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592088.6524614135</v>
+        <v>591673</v>
       </c>
       <c r="R5" t="n">
-        <v>6428553.25590604</v>
+        <v>6428568</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1163,27 +1102,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2023-12-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Nyfynd. Upptäckt av Eddy Kasselstrand.  Senast rapporterad från Västerviks kommun av Staffan Renström 1984, 500 m NV Gettersgölen, Västra Ed socken  i fuktig lågörtsgranskog. Lokalen besöktes av Stefan Kasselstrand ca 2010 men skogen var då avverkad och helt olämplig för kambräken.  Kambräken är mycket sällsynt i östra Småland och därför är det helt olämpligt att skogen avverkas.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,15 +1125,20 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>I kanten av dike i fuktig granskog.</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1214,12 +1148,7 @@
         <v>95501720</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591666.8969997162</v>
+        <v>591667</v>
       </c>
       <c r="R6" t="n">
-        <v>6428779.017716779</v>
+        <v>6428779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1345,15 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113670372</v>
+        <v>95503424</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1304,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1388,19 +1312,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591655</v>
+        <v>591607</v>
       </c>
       <c r="R7" t="n">
-        <v>6428761</v>
+        <v>6428807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1427,12 +1355,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,22 +1396,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113670167</v>
+        <v>95503476</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1433,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1503,22 +1441,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A62464 Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591656</v>
+        <v>591590</v>
       </c>
       <c r="R8" t="n">
-        <v>6428719</v>
+        <v>6428792</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,12 +1484,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,27 +1520,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113670015</v>
+        <v>95503935</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1618,22 +1570,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591670</v>
+        <v>592063</v>
       </c>
       <c r="R9" t="n">
-        <v>6428535</v>
+        <v>6428536</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1657,12 +1613,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,22 +1654,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113670087</v>
+        <v>95504020</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1691,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1733,22 +1699,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591620</v>
+        <v>592076</v>
       </c>
       <c r="R10" t="n">
-        <v>6428556</v>
+        <v>6428540</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1772,12 +1742,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1798,22 +1783,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113670366</v>
+        <v>95504230</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1820,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1848,22 +1828,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591658</v>
+        <v>592089</v>
       </c>
       <c r="R11" t="n">
-        <v>6428750</v>
+        <v>6428553</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1887,12 +1871,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1913,22 +1912,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113669977</v>
+        <v>95504253</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1949,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1963,22 +1957,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591681</v>
+        <v>592083</v>
       </c>
       <c r="R12" t="n">
-        <v>6428541</v>
+        <v>6428555</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2002,12 +2000,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,22 +2041,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113670156</v>
+        <v>95504442</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2078,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2078,22 +2086,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591620</v>
+        <v>592133</v>
       </c>
       <c r="R13" t="n">
-        <v>6428694</v>
+        <v>6428587</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2117,12 +2129,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2143,22 +2165,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113670294</v>
+        <v>95504638</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2202,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2193,22 +2210,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591656</v>
+        <v>592075</v>
       </c>
       <c r="R14" t="n">
-        <v>6428673</v>
+        <v>6428583</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2232,12 +2253,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,22 +2294,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113670131</v>
+        <v>95504828</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,7 +2331,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2308,22 +2339,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591625</v>
+        <v>592054</v>
       </c>
       <c r="R15" t="n">
-        <v>6428584</v>
+        <v>6428560</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2347,12 +2382,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2373,22 +2423,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113670476</v>
+        <v>95504946</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2460,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2423,22 +2468,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A37438, Troserum, V Ed, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591642</v>
+        <v>591993</v>
       </c>
       <c r="R16" t="n">
-        <v>6428794</v>
+        <v>6428572</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2462,12 +2511,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2021-08-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>5 + 3</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,22 +2552,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113670452</v>
+        <v>113669873</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,7 +2589,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2547,10 +2606,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591629</v>
+        <v>591698</v>
       </c>
       <c r="R17" t="n">
-        <v>6428785</v>
+        <v>6428530</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2610,15 +2669,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113670250</v>
+        <v>113669887</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2699,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2658,17 +2712,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A62464-2023, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591635</v>
+        <v>591667</v>
       </c>
       <c r="R18" t="n">
-        <v>6428785</v>
+        <v>6428681</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2713,27 +2767,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113670158</v>
+        <v>113669936</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2809,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2773,14 +2822,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A62464-2023 Troserum, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591647</v>
+        <v>591671</v>
       </c>
       <c r="R19" t="n">
-        <v>6428721</v>
+        <v>6428668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2828,27 +2877,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113669873</v>
+        <v>113669948</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2875,7 +2919,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2892,13 +2936,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591698</v>
+        <v>591682</v>
       </c>
       <c r="R20" t="n">
-        <v>6428530</v>
+        <v>6428650</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2928,6 +2972,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3 fröställningar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2955,42 +3004,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113668913</v>
+        <v>113669961</v>
       </c>
       <c r="B21" t="n">
-        <v>96830</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220686</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3003,17 +3047,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 62464-2023 Troserum, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591673</v>
+        <v>591668</v>
       </c>
       <c r="R21" t="n">
         <v>6428568</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3043,11 +3087,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-12-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Nyfynd. Upptäckt av Eddy Kasselstrand.  Senast rapporterad från Västerviks kommun av Staffan Renström 1984, 500 m NV Gettersgölen, Västra Ed socken  i fuktig lågörtsgranskog. Lokalen besöktes av Stefan Kasselstrand ca 2010 men skogen var då avverkad och helt olämplig för kambräken.  Kambräken är mycket sällsynt i östra Småland och därför är det helt olämpligt att skogen avverkas.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3060,67 +3099,61 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>I kanten av dike i fuktig granskog.</t>
-        </is>
-      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113670105</v>
+        <v>113669977</v>
       </c>
       <c r="B22" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3128,10 +3161,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591638</v>
+        <v>591681</v>
       </c>
       <c r="R22" t="n">
-        <v>6428563</v>
+        <v>6428541</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3166,17 +3199,13 @@
           <t>2023-12-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mkt</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3195,15 +3224,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113670151</v>
+        <v>113669996</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3230,7 +3254,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3243,14 +3267,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A62464-2023, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591636</v>
+        <v>591681</v>
       </c>
       <c r="R23" t="n">
-        <v>6428671</v>
+        <v>6428547</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3298,27 +3322,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113670360</v>
+        <v>113670004</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3345,7 +3364,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3362,10 +3381,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591663</v>
+        <v>591673</v>
       </c>
       <c r="R24" t="n">
-        <v>6428737</v>
+        <v>6428532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3425,15 +3444,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113670114</v>
+        <v>113670015</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3474,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3477,10 +3491,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591635</v>
+        <v>591670</v>
       </c>
       <c r="R25" t="n">
-        <v>6428574</v>
+        <v>6428535</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3513,11 +3527,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-12-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 fröställning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3545,15 +3554,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113669961</v>
+        <v>113670029</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,10 +3601,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591668</v>
+        <v>591673</v>
       </c>
       <c r="R26" t="n">
-        <v>6428568</v>
+        <v>6428534</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3660,15 +3664,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113670188</v>
+        <v>113670045</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3695,7 +3694,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3708,14 +3707,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A62464-2023, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591658</v>
+        <v>591650</v>
       </c>
       <c r="R27" t="n">
-        <v>6428758</v>
+        <v>6428558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3763,27 +3762,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113670384</v>
+        <v>113670058</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3810,7 +3804,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3827,10 +3821,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591677</v>
+        <v>591651</v>
       </c>
       <c r="R28" t="n">
-        <v>6428769</v>
+        <v>6428555</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3890,15 +3884,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113670353</v>
+        <v>113670087</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3925,7 +3914,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3942,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591678</v>
+        <v>591620</v>
       </c>
       <c r="R29" t="n">
-        <v>6428735</v>
+        <v>6428556</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3978,11 +3967,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-12-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>3 feöställningar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4010,15 +3994,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113670378</v>
+        <v>113670094</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4045,7 +4024,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4062,10 +4041,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591683</v>
+        <v>591634</v>
       </c>
       <c r="R30" t="n">
-        <v>6428757</v>
+        <v>6428558</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4125,15 +4104,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113670387</v>
+        <v>113670103</v>
       </c>
       <c r="B31" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4160,7 +4134,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4177,10 +4151,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591685</v>
+        <v>591638</v>
       </c>
       <c r="R31" t="n">
-        <v>6428778</v>
+        <v>6428563</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4240,15 +4214,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113670224</v>
+        <v>113670114</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4275,7 +4244,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4288,17 +4257,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A62464-2023, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591658</v>
+        <v>591635</v>
       </c>
       <c r="R32" t="n">
-        <v>6428780</v>
+        <v>6428574</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4332,7 +4301,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>med fröställningar</t>
+          <t>1 fröställning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4348,27 +4317,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113670094</v>
+        <v>113670120</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4395,7 +4359,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4412,10 +4376,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591634</v>
+        <v>591633</v>
       </c>
       <c r="R33" t="n">
-        <v>6428558</v>
+        <v>6428574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4475,15 +4439,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113670120</v>
+        <v>113670131</v>
       </c>
       <c r="B34" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4510,7 +4469,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4527,10 +4486,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591633</v>
+        <v>591625</v>
       </c>
       <c r="R34" t="n">
-        <v>6428574</v>
+        <v>6428584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4590,15 +4549,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113669936</v>
+        <v>113670139</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4625,7 +4579,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4638,14 +4592,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464-2023 Troserum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591671</v>
+        <v>591672</v>
       </c>
       <c r="R35" t="n">
-        <v>6428668</v>
+        <v>6428526</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4693,27 +4647,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113670139</v>
+        <v>113670140</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4740,7 +4689,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4753,14 +4702,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A62464-2023 Troserum, Sm</t>
+          <t>A 62464, Troserum, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591672</v>
+        <v>591626</v>
       </c>
       <c r="R36" t="n">
-        <v>6428526</v>
+        <v>6428625</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4808,27 +4757,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113670029</v>
+        <v>113670148</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4855,7 +4799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4872,10 +4816,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>591673</v>
+        <v>591634</v>
       </c>
       <c r="R37" t="n">
-        <v>6428534</v>
+        <v>6428642</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4908,6 +4852,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 feöställning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4935,15 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113670201</v>
+        <v>113670151</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4970,7 +4914,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4987,13 +4931,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591675</v>
+        <v>591636</v>
       </c>
       <c r="R38" t="n">
-        <v>6428765</v>
+        <v>6428671</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5050,15 +4994,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113670315</v>
+        <v>113670156</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5102,10 +5041,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591675</v>
+        <v>591620</v>
       </c>
       <c r="R39" t="n">
-        <v>6428679</v>
+        <v>6428694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5165,15 +5104,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113670103</v>
+        <v>113670158</v>
       </c>
       <c r="B40" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5200,7 +5134,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5213,14 +5147,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464-2023 Troserum, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591638</v>
+        <v>591647</v>
       </c>
       <c r="R40" t="n">
-        <v>6428563</v>
+        <v>6428721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5268,27 +5202,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113670058</v>
+        <v>113670167</v>
       </c>
       <c r="B41" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5315,7 +5244,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5328,17 +5257,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464 Troserum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591651</v>
+        <v>591656</v>
       </c>
       <c r="R41" t="n">
-        <v>6428555</v>
+        <v>6428719</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5383,27 +5312,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113670045</v>
+        <v>113670188</v>
       </c>
       <c r="B42" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5430,7 +5354,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5443,14 +5367,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464-2023, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591650</v>
+        <v>591658</v>
       </c>
       <c r="R42" t="n">
-        <v>6428558</v>
+        <v>6428758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5498,27 +5422,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113670301</v>
+        <v>113670201</v>
       </c>
       <c r="B43" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5558,17 +5477,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464-2023, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591678</v>
+        <v>591675</v>
       </c>
       <c r="R43" t="n">
-        <v>6428681</v>
+        <v>6428765</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5613,27 +5532,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113670457</v>
+        <v>113670224</v>
       </c>
       <c r="B44" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5660,7 +5574,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5673,17 +5587,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464-2023, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591637</v>
+        <v>591658</v>
       </c>
       <c r="R44" t="n">
-        <v>6428792</v>
+        <v>6428780</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5713,6 +5627,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>med fröställningar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5728,27 +5647,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113669996</v>
+        <v>113670250</v>
       </c>
       <c r="B45" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5775,7 +5689,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5788,17 +5702,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 62464, Troserum, Sm</t>
+          <t>A62464-2023, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591681</v>
+        <v>591635</v>
       </c>
       <c r="R45" t="n">
-        <v>6428547</v>
+        <v>6428785</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5843,49 +5757,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113670077</v>
+        <v>113670294</v>
       </c>
       <c r="B46" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5907,10 +5816,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591622</v>
+        <v>591656</v>
       </c>
       <c r="R46" t="n">
-        <v>6428564</v>
+        <v>6428673</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5970,15 +5879,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113669948</v>
+        <v>113670301</v>
       </c>
       <c r="B47" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6005,7 +5909,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6022,13 +5926,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>591682</v>
+        <v>591678</v>
       </c>
       <c r="R47" t="n">
-        <v>6428650</v>
+        <v>6428681</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6058,11 +5962,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-12-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>3 fröställningar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6090,15 +5989,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113670140</v>
+        <v>113670315</v>
       </c>
       <c r="B48" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6125,7 +6019,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6142,10 +6036,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591626</v>
+        <v>591675</v>
       </c>
       <c r="R48" t="n">
-        <v>6428625</v>
+        <v>6428679</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6205,42 +6099,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113669955</v>
+        <v>113670353</v>
       </c>
       <c r="B49" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6257,10 +6146,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>591675</v>
+        <v>591678</v>
       </c>
       <c r="R49" t="n">
-        <v>6428581</v>
+        <v>6428735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6293,6 +6182,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>3 feöställningar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6320,15 +6214,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113670004</v>
+        <v>113670360</v>
       </c>
       <c r="B50" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6355,7 +6244,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6372,10 +6261,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591673</v>
+        <v>591663</v>
       </c>
       <c r="R50" t="n">
-        <v>6428532</v>
+        <v>6428737</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6435,15 +6324,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113670398</v>
+        <v>113670366</v>
       </c>
       <c r="B51" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6470,7 +6354,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6487,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591671</v>
+        <v>591658</v>
       </c>
       <c r="R51" t="n">
-        <v>6428777</v>
+        <v>6428750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6550,15 +6434,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113670413</v>
+        <v>113670372</v>
       </c>
       <c r="B52" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6585,7 +6464,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6602,10 +6481,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591658</v>
+        <v>591655</v>
       </c>
       <c r="R52" t="n">
-        <v>6428792</v>
+        <v>6428761</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6665,15 +6544,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113670148</v>
+        <v>113670378</v>
       </c>
       <c r="B53" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6700,7 +6574,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6717,10 +6591,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591634</v>
+        <v>591683</v>
       </c>
       <c r="R53" t="n">
-        <v>6428642</v>
+        <v>6428757</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6753,11 +6627,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-12-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 feöställning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6785,15 +6654,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113669887</v>
+        <v>113670384</v>
       </c>
       <c r="B54" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6820,7 +6684,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6837,10 +6701,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>591667</v>
+        <v>591677</v>
       </c>
       <c r="R54" t="n">
-        <v>6428681</v>
+        <v>6428769</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6897,6 +6761,1106 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>113670387</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>591685</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6428778</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>113670398</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>591671</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6428777</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>113670413</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>591658</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6428792</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>113670419</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>591654</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6428800</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>113670425</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>591647</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6428804</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>113670452</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>591629</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6428785</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>113670457</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>591637</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6428792</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>113670476</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>591642</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6428794</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>113669955</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>591675</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6428581</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>113670077</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>A 62464, Troserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>591622</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6428564</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Västra Ed</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
